--- a/education_forms/004_technology_survey--education_forms.xlsx
+++ b/education_forms/004_technology_survey--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>classroom_survey</t>
+          <t>education_level</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>classroom_survey</t>
+          <t>What is your highest level of education completed?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>workplace_survey</t>
+          <t>technology_experience_workplace</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>workplace_survey</t>
+          <t>How would you rate your experience with technology at work?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>school_survey</t>
+          <t>technology_experience_classroom</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>school_survey</t>
+          <t>How would you rate your experience with technology in the classroom?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>technology_interest_level</t>
+          <t>technology_importance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>technology_interest_level</t>
+          <t>How important is technology to your job?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>technology_interest_level_other</t>
+          <t>technology_hobby</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>What is your favorite technology-related hobby or activity?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>technology_interest_level_other_description</t>
+          <t>technology_use_personal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>other_description</t>
+          <t>How often do you use technology for personal projects or hobbies?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>classroom_technology_level</t>
+          <t>technology_interest</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>classroom_technology_level</t>
+          <t>What is your level of interest in learning more about technology?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>classroom_technology_level_other</t>
+          <t>online_resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>Do you prefer to learn through online resources or in-person tutorials?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>workplace_technology_level</t>
+          <t>online_experience</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>workplace_technology_level</t>
+          <t>How would you rate your experience with online learning platforms?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>workplace_technology_level_other</t>
+          <t>online_use</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>How often do you use online resources for learning?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>school_technology_level</t>
+          <t>online_language</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>school_technology_level</t>
+          <t>What is your preferred language for online learning (e.g., programming languages, languages)?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,39 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>school_technology_level_other</t>
+          <t>technology_comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>Any additional comments or suggestions for improving technology education?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>technology_survey_comments</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>technology_survey_comments</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -822,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -850,153 +827,646 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>classroom_technology_level_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>classroom_1</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>classroom_1</t>
+          <t>high school</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>classroom_technology_level_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>classroom_2</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>classroom_2</t>
+          <t>some college</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>classroom_technology_level_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>classroom_3</t>
+          <t>bachelor_degree</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>classroom_3</t>
+          <t>bachelor degree</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>workplace_technology_level_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>workplace_1</t>
+          <t>master_degree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>workplace_1</t>
+          <t>master degree</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>workplace_technology_level_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>workplace_2</t>
+          <t>doctorate</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>workplace_2</t>
+          <t>doctorate</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>workplace_technology_level_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>workplace_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>workplace_3</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>school_technology_level_choices</t>
+          <t>technology_experience_workplace_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>school_1</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>school_1</t>
+          <t>beginner</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>school_technology_level_choices</t>
+          <t>technology_experience_workplace_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>school_2</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>school_2</t>
+          <t>intermediate</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>school_technology_level_choices</t>
+          <t>technology_experience_workplace_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>school_3</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>school_3</t>
+          <t>advanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>technology_experience_workplace_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>technology_experience_classroom_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>beginner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>beginner</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>technology_experience_classroom_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>intermediate</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>intermediate</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>technology_experience_classroom_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>advanced</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>advanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>technology_experience_classroom_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>technology_importance_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>not_at_all</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>not at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>technology_importance_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>somewhat</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>somewhat</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>technology_importance_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>technology_importance_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>very_important</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>very important</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>technology_use_personal_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>technology_use_personal_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>technology_use_personal_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>sometimes</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>sometimes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>technology_use_personal_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>often</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>often</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>technology_use_personal_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>technology_interest_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>not_at_all</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>not at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>technology_interest_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>somewhat</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>somewhat</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>technology_interest_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>technology_interest_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>very_important</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>very important</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>online_resources_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>online_resources_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>in_person</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>in person</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>online_experience_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>beginner</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>beginner</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>online_experience_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>intermediate</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>intermediate</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>online_experience_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>advanced</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>advanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>online_experience_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>online_use_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>online_use_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>online_use_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>sometimes</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>sometimes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>online_use_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>often</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>often</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>online_use_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>always</t>
         </is>
       </c>
     </row>
